--- a/outputs/per-fund/vc-investments-dragonfly.xlsx
+++ b/outputs/per-fund/vc-investments-dragonfly.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Dragonfly. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Dragonfly. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -30159,11 +30159,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, multicoin-capital</t>
+          <t>coinfund, dragonfly, multicoin-capital</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -30348,11 +30348,11 @@
         <v>1</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly, electric-capital, pantera, polychain</t>
+          <t>a16z-crypto, dragonfly, electric-capital, pantera, polychain, yzi-labs</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -30411,11 +30411,11 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital, paradigm, polychain</t>
+          <t>1kx, arrington-capital, coinbase-ventures, dragonfly, electric-capital, paradigm, polychain</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -30722,11 +30722,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, huobi-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -30848,11 +30848,11 @@
         <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital, pantera</t>
+          <t>arrington-capital, dragonfly, electric-capital, hashed, huobi-ventures, pantera</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -30905,11 +30905,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, polychain</t>
+          <t>digital-currency-group, dragonfly, polychain</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -30968,11 +30968,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, pantera</t>
+          <t>cmt-digital, dragonfly, pantera</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -31094,11 +31094,11 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, maven11, pantera</t>
+          <t>coinbase-ventures, dragonfly, fenbushi-capital, maven11, pantera</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -31334,11 +31334,11 @@
         <v>1</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, dragonfly</t>
+          <t>bain-capital-crypto, dragonfly, hack-vc</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -31397,11 +31397,11 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>1kx, dragonfly, hashed</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -31759,11 +31759,11 @@
         <v>2</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, pantera, paradigm, polychain</t>
+          <t>coinbase-ventures, dragonfly, fenbushi-capital, pantera, paradigm, polychain</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -31879,11 +31879,11 @@
         <v>1</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>coinfund, dragonfly</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -31942,11 +31942,11 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>coinbase-ventures, digital-currency-group, dragonfly</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -32131,11 +32131,11 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>1kx, coinfund, dragonfly</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -32190,11 +32190,11 @@
         <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, galaxy-digital, iosg-ventures</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -32253,11 +32253,11 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, galaxy-digital, iosg-ventures, yzi-labs</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -32379,11 +32379,11 @@
         <v>1</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, fenbushi-capital, hashkey-capital, iosg-ventures</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -32442,11 +32442,11 @@
         <v>1</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, multicoin-capital</t>
+          <t>coinbase-ventures, digital-currency-group, dragonfly, hashed, multicoin-capital</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -32505,11 +32505,11 @@
         <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, dragonfly, paradigm</t>
+          <t>bain-capital-crypto, dragonfly, hack-vc, paradigm</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -32568,11 +32568,11 @@
         <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>coinbase-ventures, dragonfly, huobi-ventures</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -32938,11 +32938,11 @@
         <v>1</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>1kx, coinbase-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -33064,11 +33064,11 @@
         <v>4</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>animoca-brands, animoca-brands-japan, dragonfly</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -33125,11 +33125,11 @@
         <v>1</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>alliance-dao, coinbase-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -33188,11 +33188,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>arrington-capital, dragonfly, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -33253,11 +33253,11 @@
         <v>2</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital</t>
+          <t>alameda-research, arrington-capital, dragonfly, electric-capital, galaxy-digital</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -33312,11 +33312,11 @@
         <v>1</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, dragonfly, paradigm, robot-ventures</t>
+          <t>alameda-research, coinbase-ventures, delphi-ventures, digital-currency-group, dragonfly, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -33432,11 +33432,11 @@
         <v>2</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, framework-ventures</t>
+          <t>cms-holdings, dragonfly, framework-ventures, hashed, longhash-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -33491,11 +33491,11 @@
         <v>0</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, maven11</t>
+          <t>dragonfly, galaxy-digital, maven11, parafi-capital</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -33674,11 +33674,11 @@
         <v>4</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, founders-fund, pantera</t>
+          <t>dragonfly, fenbushi-capital, founders-fund, pantera, spartan-group</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -33737,11 +33737,11 @@
         <v>0</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap, polychain, robot-ventures</t>
+          <t>dragonfly, galaxy-digital, lemniscap, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -33802,11 +33802,11 @@
         <v>3</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, polychain</t>
+          <t>cmt-digital, dragonfly, foresight-ventures, polychain</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -34046,11 +34046,11 @@
         <v>1</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital</t>
+          <t>digital-currency-group, dragonfly, electric-capital, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -34235,11 +34235,11 @@
         <v>2</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, framework-ventures</t>
+          <t>alliance-dao, dragonfly, framework-ventures, longhash-ventures</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
@@ -34294,11 +34294,11 @@
         <v>1</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, polychain</t>
+          <t>cms-holdings, dragonfly, polychain</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -34357,11 +34357,11 @@
         <v>1</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, gsr, huobi-ventures, okx-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -34420,11 +34420,11 @@
         <v>0</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, parafi-capital</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -34483,11 +34483,11 @@
         <v>3</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>animoca-brands, dragonfly, mechanism-capital, okx-ventures, sfermion</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
@@ -34603,11 +34603,11 @@
         <v>0</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, sequoia-capital</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -34666,11 +34666,11 @@
         <v>3</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>alameda-research, arrington-capital, cmt-digital, delphi-ventures, dragonfly, fenbushi-capital, hashed, sfermion</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -34729,11 +34729,11 @@
         <v>1</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, multicoin-capital</t>
+          <t>alameda-research, animoca-brands, animoca-brands-japan, dragonfly, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -34855,11 +34855,11 @@
         <v>1</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly</t>
+          <t>1kx, a16z-crypto, dragonfly, okx-ventures</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -34920,11 +34920,11 @@
         <v>2</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital</t>
+          <t>animoca-brands, coinbase-ventures, dragonfly, electric-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -35166,11 +35166,11 @@
         <v>2</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>alameda-research, cmt-digital, digital-currency-group, dragonfly, mirana-ventures</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -35227,11 +35227,11 @@
         <v>0</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly</t>
+          <t>a16z-crypto, dragonfly, mechanism-capital</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -35290,11 +35290,11 @@
         <v>3</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, fenbushi-capital, hashkey-capital</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -35347,11 +35347,11 @@
         <v>2</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>coinbase-ventures, dragonfly, hashkey-capital, huobi-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -35410,11 +35410,11 @@
         <v>1</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>cms-holdings, dragonfly, sequoia-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -35471,11 +35471,11 @@
         <v>0</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>coinbase-ventures, dragonfly, huobi-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -35534,11 +35534,11 @@
         <v>1</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>circle-ventures, coinbase-ventures, dragonfly, sequoia-capital</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -35660,11 +35660,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, multicoin-capital</t>
+          <t>alameda-research, cmt-digital, coinbase-ventures, coinfund, dragonfly, hashed, hashkey-capital, iosg-ventures, multicoin-capital, parafi-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -35723,11 +35723,11 @@
         <v>0</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, fenbushi-capital, hypersphere, iosg-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -35845,11 +35845,11 @@
         <v>1</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly</t>
+          <t>a16z-crypto, alameda-research, amber-group, circle-ventures, dragonfly, mechanism-capital</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -35908,11 +35908,11 @@
         <v>3</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, pantera</t>
+          <t>alameda-research, coinbase-ventures, dragonfly, hashed, mechanism-capital, pantera</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
@@ -35971,11 +35971,11 @@
         <v>2</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, multicoin-capital</t>
+          <t>alameda-research, coinbase-ventures, dragonfly, hashkey-capital, mirana-ventures, multicoin-capital, sfermion, solana-ventures, spartan-group, yzi-labs</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -36030,11 +36030,11 @@
         <v>0</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital</t>
+          <t>alameda-research, arrington-capital, coinfund, dragonfly, fenbushi-capital, figment-capital, hashed, hashkey-capital, huobi-ventures</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -36152,11 +36152,11 @@
         <v>1</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>alameda-research, animoca-brands, coinfund, digital-currency-group, dragonfly, galaxy-digital, sequoia-capital, spartan-group</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
@@ -36215,11 +36215,11 @@
         <v>0</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>alliance-dao, animoca-brands, cmt-digital, delphi-ventures, dragonfly, sfermion</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -36278,11 +36278,11 @@
         <v>1</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, dragonfly</t>
+          <t>a16z-crypto, animoca-brands, animoca-brands-japan, coinbase-ventures, dragonfly, foresight-ventures, hashed, polygon-ventures</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -36337,11 +36337,11 @@
         <v>2</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, lemniscap, polychain</t>
+          <t>alameda-research, amber-group, coinbase-ventures, dragonfly, jump-crypto, lemniscap, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -36463,11 +36463,11 @@
         <v>0</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, pantera</t>
+          <t>coinbase-ventures, dragonfly, galaxy-digital, pantera, sfermion, solana-ventures</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -36522,11 +36522,11 @@
         <v>0</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>alameda-research, dragonfly, jump-crypto, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -36585,11 +36585,11 @@
         <v>1</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>coinbase-ventures, dragonfly, parafi-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
@@ -36646,11 +36646,11 @@
         <v>1</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, mirana-ventures</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -36709,11 +36709,11 @@
         <v>1</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, pantera</t>
+          <t>alameda-research, coinbase-ventures, dragonfly, pantera, solana-ventures</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
@@ -36774,11 +36774,11 @@
         <v>0</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>coinfund, dragonfly, mh-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
@@ -36837,11 +36837,11 @@
         <v>0</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, maven11</t>
+          <t>animoca-brands, dragonfly, maven11</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
@@ -36900,11 +36900,11 @@
         <v>3</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap</t>
+          <t>dragonfly, iosg-ventures, jump-crypto, lemniscap, parafi-capital, sevenx-ventures</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
@@ -36963,11 +36963,11 @@
         <v>1</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, electric-capital, lemniscap</t>
+          <t>dragonfly, electric-capital, jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
@@ -37022,11 +37022,11 @@
         <v>1</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, hashed, parafi-capital</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -37085,11 +37085,11 @@
         <v>0</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, parafi-capital</t>
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr">
@@ -37148,11 +37148,11 @@
         <v>1</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, gsr, parafi-capital</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
@@ -37335,11 +37335,11 @@
         <v>2</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>animoca-brands, dragonfly, mechanism-capital, polygon-ventures</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
@@ -37394,11 +37394,11 @@
         <v>1</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, robot-ventures</t>
+          <t>alliance-dao, dragonfly, robot-ventures</t>
         </is>
       </c>
       <c r="M119" s="7" t="inlineStr">
@@ -37459,11 +37459,11 @@
         <v>1</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, sequoia-capital</t>
         </is>
       </c>
       <c r="M120" s="7" t="inlineStr">
@@ -37522,11 +37522,11 @@
         <v>0</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>cmt-digital, dragonfly, mirana-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M121" s="7" t="inlineStr">
@@ -37585,11 +37585,11 @@
         <v>2</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, polychain</t>
+          <t>coinbase-ventures, dragonfly, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M122" s="7" t="inlineStr">
@@ -37648,11 +37648,11 @@
         <v>0</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly, pantera</t>
+          <t>a16z-crypto, dragonfly, pantera, sfermion</t>
         </is>
       </c>
       <c r="M123" s="7" t="inlineStr">
@@ -37711,11 +37711,11 @@
         <v>2</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap</t>
+          <t>dragonfly, galaxy-digital, lemniscap</t>
         </is>
       </c>
       <c r="M124" s="7" t="inlineStr">
@@ -37774,11 +37774,11 @@
         <v>1</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>big-brain-holdings, dragonfly, solana-ventures</t>
         </is>
       </c>
       <c r="M125" s="7" t="inlineStr">
@@ -37839,11 +37839,11 @@
         <v>1</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, foresight-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M126" s="7" t="inlineStr">
@@ -37902,11 +37902,11 @@
         <v>0</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, lemniscap</t>
+          <t>alameda-research, coinbase-ventures, dragonfly, hashed, lemniscap, polygon-ventures</t>
         </is>
       </c>
       <c r="M127" s="7" t="inlineStr">
@@ -37965,11 +37965,11 @@
         <v>0</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>circle-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr">
@@ -38089,11 +38089,11 @@
         <v>0</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, galaxy-digital, jump-crypto</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr">
@@ -38152,11 +38152,11 @@
         <v>0</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, pantera</t>
+          <t>alameda-research, amber-group, dragonfly, foresight-ventures, gsr, iosg-ventures, jump-crypto, mirana-ventures, pantera, sequoia-capital, sevenx-ventures</t>
         </is>
       </c>
       <c r="M131" s="7" t="inlineStr">
@@ -38337,11 +38337,11 @@
         <v>1</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>1kx, coinbase-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -38400,11 +38400,11 @@
         <v>0</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, gsr</t>
         </is>
       </c>
       <c r="M135" s="7" t="inlineStr">
@@ -38463,11 +38463,11 @@
         <v>0</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>circle-ventures, digital-currency-group, dragonfly</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -38528,11 +38528,11 @@
         <v>0</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, electric-capital</t>
+          <t>coinbase-ventures, dragonfly, electric-capital, gsr, jump-crypto</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
@@ -38591,11 +38591,11 @@
         <v>2</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>animoca-brands, dragonfly, longhash-ventures, mechanism-capital, sfermion</t>
         </is>
       </c>
       <c r="M138" s="7" t="inlineStr">
@@ -38654,11 +38654,11 @@
         <v>0</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, gsr</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -38839,11 +38839,11 @@
         <v>0</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>delphi-ventures, dragonfly, mechanism-capital</t>
         </is>
       </c>
       <c r="M142" s="7" t="inlineStr">
@@ -38902,11 +38902,11 @@
         <v>0</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>delphi-ventures, dragonfly, parafi-capital</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -38961,11 +38961,11 @@
         <v>0</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, sequoia-capital</t>
         </is>
       </c>
       <c r="M144" s="7" t="inlineStr">
@@ -39270,11 +39270,11 @@
         <v>1</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, paradigm</t>
+          <t>dragonfly, hypersphere, paradigm</t>
         </is>
       </c>
       <c r="M149" s="7" t="inlineStr">
@@ -39329,11 +39329,11 @@
         <v>0</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>digital-currency-group, dragonfly, mirana-ventures</t>
         </is>
       </c>
       <c r="M150" s="7" t="inlineStr">
@@ -39392,11 +39392,11 @@
         <v>0</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, multicoin-capital</t>
+          <t>dragonfly, multicoin-capital, polygon-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -39457,11 +39457,11 @@
         <v>2</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly</t>
+          <t>a16z-crypto, blockchain-capital, dragonfly</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -39520,11 +39520,11 @@
         <v>0</v>
       </c>
       <c r="K153" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>circle-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M153" s="7" t="inlineStr">
@@ -39583,11 +39583,11 @@
         <v>1</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, polygon-ventures, sfermion</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -39701,11 +39701,11 @@
         <v>2</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>1kx, circle-ventures, coinbase-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -39760,11 +39760,11 @@
         <v>2</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>1kx, alliance-dao, dragonfly, sequoia-capital</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr">
@@ -39945,11 +39945,11 @@
         <v>1</v>
       </c>
       <c r="K160" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, mirana-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M160" s="7" t="inlineStr">
@@ -40071,11 +40071,11 @@
         <v>1</v>
       </c>
       <c r="K162" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>animoca-brands, dragonfly, galaxy-digital, gsr, spartan-group</t>
         </is>
       </c>
       <c r="M162" s="7" t="inlineStr">
@@ -40323,11 +40323,11 @@
         <v>2</v>
       </c>
       <c r="K166" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, pantera</t>
+          <t>dragonfly, hack-vc, pantera</t>
         </is>
       </c>
       <c r="M166" s="7" t="inlineStr">
@@ -40386,11 +40386,11 @@
         <v>1</v>
       </c>
       <c r="K167" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>cmt-digital, delphi-ventures, dragonfly, gsr, mirana-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M167" s="7" t="inlineStr">
@@ -40567,11 +40567,11 @@
         <v>1</v>
       </c>
       <c r="K170" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>circle-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M170" s="7" t="inlineStr">
@@ -40626,11 +40626,11 @@
         <v>1</v>
       </c>
       <c r="K171" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly</t>
+          <t>a16z-crypto, arrington-capital, dragonfly, mechanism-capital</t>
         </is>
       </c>
       <c r="M171" s="7" t="inlineStr">
@@ -40878,11 +40878,11 @@
         <v>0</v>
       </c>
       <c r="K175" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>coinfund, dragonfly</t>
         </is>
       </c>
       <c r="M175" s="7" t="inlineStr">
@@ -40943,11 +40943,11 @@
         <v>3</v>
       </c>
       <c r="K176" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, yzi-labs</t>
         </is>
       </c>
       <c r="M176" s="7" t="inlineStr">
@@ -41006,11 +41006,11 @@
         <v>2</v>
       </c>
       <c r="K177" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital, founders-fund</t>
+          <t>dragonfly, figment-capital, founders-fund, sevenx-ventures</t>
         </is>
       </c>
       <c r="M177" s="7" t="inlineStr">
@@ -41065,11 +41065,11 @@
         <v>1</v>
       </c>
       <c r="K178" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly, maven11</t>
+          <t>delphi-ventures, dragonfly, maven11, okx-ventures</t>
         </is>
       </c>
       <c r="M178" s="7" t="inlineStr">
@@ -41128,11 +41128,11 @@
         <v>1</v>
       </c>
       <c r="K179" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, pantera</t>
+          <t>dragonfly, foresight-ventures, mh-ventures, pantera, spartan-group</t>
         </is>
       </c>
       <c r="M179" s="7" t="inlineStr">
@@ -41185,11 +41185,11 @@
         <v>0</v>
       </c>
       <c r="K180" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, dragonfly</t>
+          <t>a16z-crypto, coinbase-ventures, dragonfly, foresight-ventures, hashed, iosg-ventures, sfermion</t>
         </is>
       </c>
       <c r="M180" s="7" t="inlineStr">
@@ -41246,11 +41246,11 @@
         <v>1</v>
       </c>
       <c r="K181" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, dragonfly</t>
+          <t>a16z-crypto, arrington-capital, dragonfly, mechanism-capital</t>
         </is>
       </c>
       <c r="M181" s="7" t="inlineStr">
@@ -41372,11 +41372,11 @@
         <v>1</v>
       </c>
       <c r="K183" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>cms-holdings, dragonfly, sequoia-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M183" s="7" t="inlineStr">
@@ -41435,11 +41435,11 @@
         <v>1</v>
       </c>
       <c r="K184" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>circle-ventures, dragonfly, polygon-ventures</t>
         </is>
       </c>
       <c r="M184" s="7" t="inlineStr">
@@ -41498,11 +41498,11 @@
         <v>1</v>
       </c>
       <c r="K185" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, founders-fund</t>
+          <t>dragonfly, founders-fund, parafi-capital</t>
         </is>
       </c>
       <c r="M185" s="7" t="inlineStr">
@@ -41561,11 +41561,11 @@
         <v>3</v>
       </c>
       <c r="K186" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, dragonfly, figment-capital, founders-fund</t>
+          <t>alliance-dao, cyber-fund, dragonfly, figment-capital, foresight-ventures, founders-fund, hashkey-capital, longhash-ventures, mirana-ventures, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M186" s="7" t="inlineStr">
@@ -41687,11 +41687,11 @@
         <v>1</v>
       </c>
       <c r="K188" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital, robot-ventures</t>
+          <t>big-brain-holdings, dragonfly, figment-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M188" s="7" t="inlineStr">
@@ -41750,11 +41750,11 @@
         <v>1</v>
       </c>
       <c r="K189" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, hashkey-capital, okx-ventures</t>
         </is>
       </c>
       <c r="M189" s="7" t="inlineStr">
@@ -41872,11 +41872,11 @@
         <v>1</v>
       </c>
       <c r="K191" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, founders-fund</t>
+          <t>dragonfly, founders-fund, sequoia-capital</t>
         </is>
       </c>
       <c r="M191" s="7" t="inlineStr">
@@ -41935,11 +41935,11 @@
         <v>1</v>
       </c>
       <c r="K192" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, robot-ventures</t>
+          <t>cmt-digital, dragonfly, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M192" s="7" t="inlineStr">
@@ -42055,11 +42055,11 @@
         <v>1</v>
       </c>
       <c r="K194" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, founders-fund</t>
+          <t>blockchain-capital, coinbase-ventures, dragonfly, founders-fund, parafi-capital</t>
         </is>
       </c>
       <c r="M194" s="7" t="inlineStr">
@@ -42118,11 +42118,11 @@
         <v>2</v>
       </c>
       <c r="K195" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, dragonfly</t>
+          <t>bain-capital-crypto, coinbase-ventures, dragonfly, hack-vc</t>
         </is>
       </c>
       <c r="M195" s="7" t="inlineStr">
@@ -42236,11 +42236,11 @@
         <v>3</v>
       </c>
       <c r="K197" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>big-brain-holdings, dragonfly, galaxy-digital, hypersphere, parafi-capital</t>
         </is>
       </c>
       <c r="M197" s="7" t="inlineStr">
@@ -42425,11 +42425,11 @@
         <v>1</v>
       </c>
       <c r="K200" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, foresight-ventures</t>
         </is>
       </c>
       <c r="M200" s="7" t="inlineStr">
@@ -42486,11 +42486,11 @@
         <v>2</v>
       </c>
       <c r="K201" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly, multicoin-capital</t>
+          <t>borderless-capital, delphi-ventures, dragonfly, gsr, mh-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M201" s="7" t="inlineStr">
@@ -42549,11 +42549,11 @@
         <v>1</v>
       </c>
       <c r="K202" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, mirana-ventures</t>
         </is>
       </c>
       <c r="M202" s="7" t="inlineStr">
@@ -42608,11 +42608,11 @@
         <v>0</v>
       </c>
       <c r="K203" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>animoca-brands, digital-currency-group, dragonfly, sfermion</t>
         </is>
       </c>
       <c r="M203" s="7" t="inlineStr">
@@ -42797,11 +42797,11 @@
         <v>1</v>
       </c>
       <c r="K206" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly</t>
+          <t>circle-ventures, coinbase-ventures, dragonfly</t>
         </is>
       </c>
       <c r="M206" s="7" t="inlineStr">
@@ -42915,11 +42915,11 @@
         <v>2</v>
       </c>
       <c r="K208" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>cms-holdings, dragonfly, hashkey-capital, mirana-ventures</t>
         </is>
       </c>
       <c r="M208" s="7" t="inlineStr">
@@ -42978,11 +42978,11 @@
         <v>2</v>
       </c>
       <c r="K209" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>circle-ventures, digital-currency-group, dragonfly</t>
         </is>
       </c>
       <c r="M209" s="7" t="inlineStr">
@@ -43039,11 +43039,11 @@
         <v>1</v>
       </c>
       <c r="K210" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, founders-fund</t>
+          <t>blockchain-capital, coinbase-ventures, dragonfly, founders-fund</t>
         </is>
       </c>
       <c r="M210" s="7" t="inlineStr">
@@ -43102,11 +43102,11 @@
         <v>1</v>
       </c>
       <c r="K211" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, galaxy-digital</t>
         </is>
       </c>
       <c r="M211" s="7" t="inlineStr">
@@ -43165,11 +43165,11 @@
         <v>1</v>
       </c>
       <c r="K212" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, framework-ventures</t>
+          <t>big-brain-holdings, cmt-digital, dragonfly, framework-ventures</t>
         </is>
       </c>
       <c r="M212" s="7" t="inlineStr">
@@ -43228,11 +43228,11 @@
         <v>1</v>
       </c>
       <c r="K213" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, hashkey-capital, mirana-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M213" s="7" t="inlineStr">
@@ -43403,11 +43403,11 @@
         <v>1</v>
       </c>
       <c r="K216" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, mirana-ventures</t>
         </is>
       </c>
       <c r="M216" s="7" t="inlineStr">
@@ -43533,11 +43533,11 @@
         <v>1</v>
       </c>
       <c r="K218" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, galaxy-digital</t>
         </is>
       </c>
       <c r="M218" s="7" t="inlineStr">
@@ -43596,11 +43596,11 @@
         <v>2</v>
       </c>
       <c r="K219" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>dragonfly, mirana-ventures</t>
         </is>
       </c>
       <c r="M219" s="7" t="inlineStr">
@@ -53851,19 +53851,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -53871,7 +53871,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
